--- a/aircraft/reports/sightings-over-time-monthly.xlsx
+++ b/aircraft/reports/sightings-over-time-monthly.xlsx
@@ -1027,7 +1027,7 @@
         <v>45870</v>
       </c>
       <c r="B74" t="n">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>

--- a/aircraft/reports/sightings-over-time-monthly.xlsx
+++ b/aircraft/reports/sightings-over-time-monthly.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,6 +1030,14 @@
         <v>376</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aircraft/reports/sightings-over-time-monthly.xlsx
+++ b/aircraft/reports/sightings-over-time-monthly.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B75"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1027,15 +1027,7 @@
         <v>45870</v>
       </c>
       <c r="B74" t="n">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
-        <v>45901</v>
-      </c>
-      <c r="B75" t="n">
-        <v>1</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>

--- a/aircraft/reports/sightings-over-time-monthly.xlsx
+++ b/aircraft/reports/sightings-over-time-monthly.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1027,7 +1027,15 @@
         <v>45870</v>
       </c>
       <c r="B74" t="n">
-        <v>371</v>
+        <v>376</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B75" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/aircraft/reports/sightings-over-time-monthly.xlsx
+++ b/aircraft/reports/sightings-over-time-monthly.xlsx
@@ -1035,7 +1035,7 @@
         <v>45901</v>
       </c>
       <c r="B75" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/aircraft/reports/sightings-over-time-monthly.xlsx
+++ b/aircraft/reports/sightings-over-time-monthly.xlsx
@@ -1035,7 +1035,7 @@
         <v>45901</v>
       </c>
       <c r="B75" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/aircraft/reports/sightings-over-time-monthly.xlsx
+++ b/aircraft/reports/sightings-over-time-monthly.xlsx
@@ -1035,7 +1035,7 @@
         <v>45901</v>
       </c>
       <c r="B75" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
